--- a/data/decontamination/assessment/contamination_by_lineage.xlsx
+++ b/data/decontamination/assessment/contamination_by_lineage.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/Tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Asgard_Eukaryote_Data/data/decontamination/assessment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6829FF9D-240B-8444-B4ED-1DAF3B6993F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86AA72EE-AD67-4E4D-A560-D22F557DB20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17600" xr2:uid="{148C4358-23B8-494B-B9A7-71B935512AA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -135,10 +135,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,7 +522,7 @@
       <c r="E2" s="1">
         <v>0</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="3">
         <v>0</v>
       </c>
     </row>
@@ -541,7 +542,7 @@
       <c r="E3" s="1">
         <v>0</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="3">
         <v>0</v>
       </c>
     </row>
@@ -561,7 +562,7 @@
       <c r="E4" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="3">
         <v>0</v>
       </c>
     </row>
@@ -581,7 +582,7 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="3">
         <v>0</v>
       </c>
     </row>
@@ -601,7 +602,7 @@
       <c r="E6" s="1">
         <v>297</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="3">
         <f>E6/D6*100</f>
         <v>63.326226012793171</v>
       </c>
@@ -622,7 +623,7 @@
       <c r="E7" s="1">
         <v>14</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="3">
         <f>E7/D7*100</f>
         <v>2.9850746268656714</v>
       </c>
@@ -643,7 +644,7 @@
       <c r="E8" s="1">
         <v>120</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="3">
         <f>E8/D8*100</f>
         <v>25.586353944562902</v>
       </c>
@@ -664,7 +665,7 @@
       <c r="E9" s="1">
         <v>81</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="3">
         <f>E9/D9*100</f>
         <v>17.270788912579956</v>
       </c>
@@ -685,7 +686,7 @@
       <c r="E10" s="1">
         <v>0</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="3">
         <v>0</v>
       </c>
     </row>
@@ -705,7 +706,7 @@
       <c r="E11" s="1">
         <v>0</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="3">
         <v>0</v>
       </c>
     </row>
@@ -725,7 +726,7 @@
       <c r="E12" s="1">
         <v>0</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="3">
         <v>0</v>
       </c>
     </row>
@@ -745,7 +746,7 @@
       <c r="E13" s="1">
         <v>0</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="3">
         <v>0</v>
       </c>
     </row>
@@ -765,7 +766,7 @@
       <c r="E14" s="1">
         <v>143</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="3">
         <f>E14/D14*100</f>
         <v>30.49040511727079</v>
       </c>
@@ -786,7 +787,7 @@
       <c r="E15" s="1">
         <v>5</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="3">
         <f t="shared" ref="F15:F21" si="0">E15/D15*100</f>
         <v>1.0660980810234542</v>
       </c>
@@ -807,7 +808,7 @@
       <c r="E16" s="1">
         <v>58</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="3">
         <f t="shared" si="0"/>
         <v>12.366737739872068</v>
       </c>
@@ -828,7 +829,7 @@
       <c r="E17" s="1">
         <v>25</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="3">
         <f t="shared" si="0"/>
         <v>5.3304904051172706</v>
       </c>
@@ -849,7 +850,7 @@
       <c r="E18" s="1">
         <v>1</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="3">
         <f t="shared" si="0"/>
         <v>0.21459227467811159</v>
       </c>
@@ -870,7 +871,7 @@
       <c r="E19" s="1">
         <v>0</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -891,7 +892,7 @@
       <c r="E20" s="1">
         <v>6</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="3">
         <f t="shared" si="0"/>
         <v>1.2875536480686696</v>
       </c>
@@ -912,7 +913,7 @@
       <c r="E21" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="3">
         <f t="shared" si="0"/>
         <v>0.42918454935622319</v>
       </c>
@@ -933,7 +934,7 @@
       <c r="E22" s="1">
         <v>214</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="3">
         <f>E22/D22*100</f>
         <v>45.628997867803839</v>
       </c>
@@ -954,7 +955,7 @@
       <c r="E23" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="3">
         <f t="shared" ref="F23:F25" si="1">E23/D23*100</f>
         <v>0.42643923240938164</v>
       </c>
@@ -975,7 +976,7 @@
       <c r="E24" s="1">
         <v>67</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="3">
         <f t="shared" si="1"/>
         <v>14.285714285714285</v>
       </c>
@@ -996,7 +997,7 @@
       <c r="E25" s="1">
         <v>70</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="3">
         <f t="shared" si="1"/>
         <v>14.925373134328357</v>
       </c>
@@ -1017,7 +1018,7 @@
       <c r="E26" s="1">
         <v>0</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1037,7 +1038,7 @@
       <c r="E27" s="1">
         <v>0</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1057,7 +1058,7 @@
       <c r="E28" s="1">
         <v>0</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1077,7 +1078,7 @@
       <c r="E29" s="1">
         <v>0</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1097,7 +1098,7 @@
       <c r="E30" s="1">
         <v>205</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="3">
         <f>E30/D30*100</f>
         <v>43.710021321961619</v>
       </c>
@@ -1118,7 +1119,7 @@
       <c r="E31" s="1">
         <v>3</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="3">
         <f t="shared" ref="F31:F33" si="2">E31/D31*100</f>
         <v>0.63965884861407252</v>
       </c>
@@ -1139,7 +1140,7 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="3">
         <f t="shared" si="2"/>
         <v>12.793176972281451</v>
       </c>
@@ -1160,7 +1161,7 @@
       <c r="E33" s="1">
         <v>46</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="3">
         <f t="shared" si="2"/>
         <v>9.8081023454157776</v>
       </c>
